--- a/02table/TableS2_MPH_of_seeding_adult_traits.xlsx
+++ b/02table/TableS2_MPH_of_seeding_adult_traits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E2F557-2095-0D4F-956D-2EC936BF61C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B2EA0F-4D93-7242-84D9-328D65817A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="620" windowWidth="38400" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/02table/TableS2_MPH_of_seeding_adult_traits.xlsx
+++ b/02table/TableS2_MPH_of_seeding_adult_traits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B2EA0F-4D93-7242-84D9-328D65817A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94797E5-7C2C-CC4B-AB34-99490C29410E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1845,10 +1845,10 @@
     <t>PH</t>
   </si>
   <si>
-    <t>Table S2 Mid-parent heterosis (MPH) for seedling and adult traits.</t>
-  </si>
-  <si>
     <t>FW, fresh weight (FW); ADW, average dry weight (ADW); ML, mesocotyl length; RL, root length; SL, seedling length; pSL, partial seedling length; TL, total length; ERN, ear row number; PH, plant height; EH, ear height; KR, kernels per row; AGY, average grain yield.</t>
+  </si>
+  <si>
+    <t>Table S2. Mid-parent heterosis (MPH) for seedling and adult traits.</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2248,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -26486,7 +26486,7 @@
     </row>
     <row r="594" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A594" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
